--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 07/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU09_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 07/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU09_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.81981</v>
+        <v>16.63902</v>
       </c>
       <c r="D2" t="n">
-        <v>16.52872</v>
+        <v>16.36758</v>
       </c>
       <c r="E2" t="n">
-        <v>16.7453</v>
+        <v>16.45919</v>
       </c>
       <c r="F2" t="n">
-        <v>43.34283</v>
+        <v>42.49772</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05104</v>
+        <v>0.0499</v>
       </c>
       <c r="H2" t="n">
-        <v>1.86691</v>
+        <v>1.80571</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.73986</v>
+        <v>16.41913</v>
       </c>
       <c r="D3" t="n">
-        <v>16.38349</v>
+        <v>16.19476</v>
       </c>
       <c r="E3" t="n">
-        <v>16.46851</v>
+        <v>16.20305</v>
       </c>
       <c r="F3" t="n">
-        <v>42.05768</v>
+        <v>41.90102</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05019</v>
+        <v>0.04945</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83512</v>
+        <v>1.79871</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.65151</v>
+        <v>16.86286</v>
       </c>
       <c r="D4" t="n">
-        <v>16.14178</v>
+        <v>16.33747</v>
       </c>
       <c r="E4" t="n">
-        <v>16.91522</v>
+        <v>16.59056</v>
       </c>
       <c r="F4" t="n">
-        <v>41.67842</v>
+        <v>43.13034</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0496</v>
+        <v>0.04901</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8292</v>
+        <v>1.79658</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.59913</v>
+        <v>16.29125</v>
       </c>
       <c r="D5" t="n">
-        <v>16.30139</v>
+        <v>16.22441</v>
       </c>
       <c r="E5" t="n">
-        <v>16.41157</v>
+        <v>16.25142</v>
       </c>
       <c r="F5" t="n">
-        <v>41.78153</v>
+        <v>41.98004</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05028</v>
+        <v>0.05001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.77374</v>
+        <v>1.78145</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.64587</v>
+        <v>16.76134</v>
       </c>
       <c r="D6" t="n">
-        <v>16.3239</v>
+        <v>16.24224</v>
       </c>
       <c r="E6" t="n">
-        <v>16.54217</v>
+        <v>16.48054</v>
       </c>
       <c r="F6" t="n">
-        <v>40.83903</v>
+        <v>42.8008</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05023</v>
+        <v>0.04848</v>
       </c>
       <c r="H6" t="n">
-        <v>1.79733</v>
+        <v>1.77031</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.57921</v>
+        <v>16.65107</v>
       </c>
       <c r="D7" t="n">
-        <v>16.12552</v>
+        <v>16.35253</v>
       </c>
       <c r="E7" t="n">
-        <v>16.69044</v>
+        <v>16.39028</v>
       </c>
       <c r="F7" t="n">
-        <v>41.63718</v>
+        <v>42.39687</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04951</v>
+        <v>0.05009</v>
       </c>
       <c r="H7" t="n">
-        <v>1.83156</v>
+        <v>1.76455</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.30495</v>
+        <v>16.73485</v>
       </c>
       <c r="D8" t="n">
-        <v>16.56074</v>
+        <v>16.14202</v>
       </c>
       <c r="E8" t="n">
-        <v>16.56671</v>
+        <v>16.59724</v>
       </c>
       <c r="F8" t="n">
-        <v>41.66869</v>
+        <v>42.11637</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04934</v>
+        <v>0.05145</v>
       </c>
       <c r="H8" t="n">
-        <v>1.79246</v>
+        <v>1.85399</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.64738</v>
+        <v>16.53631</v>
       </c>
       <c r="D9" t="n">
-        <v>16.01659</v>
+        <v>16.16117</v>
       </c>
       <c r="E9" t="n">
-        <v>16.62568</v>
+        <v>16.36575</v>
       </c>
       <c r="F9" t="n">
-        <v>41.58607</v>
+        <v>41.26187</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0487</v>
+        <v>0.0492</v>
       </c>
       <c r="H9" t="n">
-        <v>1.76861</v>
+        <v>1.79168</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.49591</v>
+        <v>16.66182</v>
       </c>
       <c r="D10" t="n">
-        <v>16.56084</v>
+        <v>16.63411</v>
       </c>
       <c r="E10" t="n">
-        <v>16.31415</v>
+        <v>16.64664</v>
       </c>
       <c r="F10" t="n">
-        <v>41.85252</v>
+        <v>41.85794</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04969</v>
+        <v>0.04983</v>
       </c>
       <c r="H10" t="n">
-        <v>1.79155</v>
+        <v>1.78106</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60995</v>
+        <v>0.59673</v>
       </c>
       <c r="D12" t="n">
-        <v>1.09941</v>
+        <v>1.11499</v>
       </c>
     </row>
     <row r="13">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.60754</v>
+        <v>0.58531</v>
       </c>
       <c r="D13" t="n">
-        <v>1.12123</v>
+        <v>1.1205</v>
       </c>
     </row>
     <row r="14">
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.60001</v>
+        <v>0.60612</v>
       </c>
       <c r="D14" t="n">
-        <v>1.11341</v>
+        <v>1.09256</v>
       </c>
     </row>
     <row r="15">
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.59521</v>
+        <v>0.60061</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0907</v>
+        <v>1.11019</v>
       </c>
     </row>
     <row r="16">
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.60371</v>
+        <v>0.60072</v>
       </c>
       <c r="D16" t="n">
-        <v>1.10609</v>
+        <v>1.08553</v>
       </c>
     </row>
     <row r="17">
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.59714</v>
+        <v>0.60577</v>
       </c>
       <c r="D17" t="n">
-        <v>1.07925</v>
+        <v>1.11395</v>
       </c>
     </row>
     <row r="18">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.59395</v>
+        <v>0.60189</v>
       </c>
       <c r="D18" t="n">
-        <v>1.08701</v>
+        <v>1.11744</v>
       </c>
     </row>
     <row r="19">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.61312</v>
+        <v>0.59522</v>
       </c>
       <c r="D19" t="n">
-        <v>1.11104</v>
+        <v>1.11665</v>
       </c>
     </row>
     <row r="20">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.59001</v>
+        <v>0.60795</v>
       </c>
       <c r="D20" t="n">
-        <v>1.12018</v>
+        <v>1.0973</v>
       </c>
     </row>
   </sheetData>
